--- a/data/trans_dic/P2A_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P2A_R-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares que tienen personas con alguna condición, enfermedad crónica o limitación</t>
+          <t>Hogares que tienen personas con alguna condición, enfermedad crónica o limitación (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>44,77; 52,3</t>
+          <t>44,47; 52,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>56,92; 64,05</t>
+          <t>56,69; 64,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>48,84; 56,86</t>
+          <t>49,13; 57,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>40,27; 49,04</t>
+          <t>40,61; 49,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>59,33; 66,22</t>
+          <t>59,44; 66,89</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,14; 72,57</t>
+          <t>64,98; 72,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>61,41; 68,77</t>
+          <t>61,69; 69,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>34,46; 49,94</t>
+          <t>35,99; 50,06</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>53,12; 58,38</t>
+          <t>53,32; 58,26</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>62,08; 67,17</t>
+          <t>62,13; 67,56</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>56,59; 61,97</t>
+          <t>56,55; 61,97</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>39,56; 48,24</t>
+          <t>39,8; 48,21</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>45,54; 51,98</t>
+          <t>45,24; 51,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>51,27; 57,43</t>
+          <t>51,1; 57,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>48,37; 54,73</t>
+          <t>48,75; 55,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17,89; 42,35</t>
+          <t>15,21; 42,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>62,05; 68,11</t>
+          <t>62,0; 68,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>68,42; 74,23</t>
+          <t>67,89; 74,05</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>62,65; 68,38</t>
+          <t>62,52; 68,66</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>46,6; 52,2</t>
+          <t>46,68; 52,38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>54,78; 59,32</t>
+          <t>54,72; 59,16</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>60,49; 65,06</t>
+          <t>60,54; 65,03</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>56,5; 61,02</t>
+          <t>56,47; 60,84</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>26,64; 46,05</t>
+          <t>26,78; 45,91</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>45,15; 53,06</t>
+          <t>45,5; 53,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>46,37; 53,84</t>
+          <t>46,21; 54,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>44,94; 52,75</t>
+          <t>44,76; 52,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>36,22; 45,47</t>
+          <t>36,94; 45,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>60,2; 67,5</t>
+          <t>59,95; 67,14</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>64,04; 70,86</t>
+          <t>64,2; 70,82</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>56,45; 63,79</t>
+          <t>56,53; 63,69</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>40,48; 75,47</t>
+          <t>39,88; 76,84</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>53,79; 59,25</t>
+          <t>53,91; 59,44</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>56,3; 61,54</t>
+          <t>56,67; 61,84</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>52,04; 57,27</t>
+          <t>51,77; 56,88</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>40,65; 65,97</t>
+          <t>40,22; 65,54</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>43,3; 49,7</t>
+          <t>43,52; 49,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>54,62; 61,16</t>
+          <t>54,29; 60,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>52,12; 58,46</t>
+          <t>52,32; 58,39</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34,57; 41,68</t>
+          <t>35,02; 41,9</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>60,35; 66,44</t>
+          <t>59,88; 66,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,57; 71,43</t>
+          <t>65,54; 71,43</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>60,3; 66,34</t>
+          <t>60,31; 66,56</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>34,04; 46,21</t>
+          <t>34,7; 46,71</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>53,2; 57,57</t>
+          <t>52,94; 57,47</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>61,27; 65,58</t>
+          <t>61,07; 65,57</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>57,37; 61,83</t>
+          <t>57,35; 61,68</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>35,57; 43,12</t>
+          <t>35,79; 43,2</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>46,39; 50,01</t>
+          <t>46,41; 49,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>53,97; 57,43</t>
+          <t>53,99; 57,34</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>50,46; 54,0</t>
+          <t>50,52; 53,9</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30,22; 41,85</t>
+          <t>29,55; 41,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>62,17; 65,77</t>
+          <t>62,3; 65,55</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>67,55; 70,8</t>
+          <t>67,7; 70,8</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>62,12; 65,31</t>
+          <t>62,21; 65,41</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>44,17; 58,07</t>
+          <t>44,01; 58,13</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>54,87; 57,41</t>
+          <t>54,92; 57,42</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>61,35; 63,74</t>
+          <t>61,46; 63,82</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>56,91; 59,33</t>
+          <t>57,0; 59,29</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>39,27; 48,31</t>
+          <t>39,36; 47,74</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares que tienen personas con alguna condición, enfermedad crónica o limitación</t>
+          <t>Hogares que tienen personas con alguna condición, enfermedad crónica o limitación (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>310728; 362990</t>
+          <t>308637; 364262</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>400406; 450557</t>
+          <t>398779; 451848</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>329589; 383674</t>
+          <t>331525; 385093</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>255916; 311618</t>
+          <t>258070; 313631</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>408377; 455841</t>
+          <t>409157; 460426</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>454092; 505842</t>
+          <t>452926; 504629</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>413204; 462719</t>
+          <t>415093; 465442</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>249924; 362229</t>
+          <t>261082; 363125</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>734314; 807038</t>
+          <t>737037; 805344</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>869384; 940697</t>
+          <t>870207; 946130</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>762655; 835174</t>
+          <t>762039; 835145</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>538317; 656469</t>
+          <t>541519; 656008</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>437976; 499956</t>
+          <t>435150; 497966</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>521916; 584594</t>
+          <t>520121; 584564</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>494580; 559590</t>
+          <t>498445; 563291</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>213344; 505142</t>
+          <t>181488; 503370</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>600914; 659614</t>
+          <t>600389; 662363</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>706176; 766154</t>
+          <t>700743; 764296</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>653415; 713192</t>
+          <t>651986; 716049</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>446744; 500387</t>
+          <t>447500; 502155</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1057414; 1145059</t>
+          <t>1056142; 1141980</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1240068; 1333911</t>
+          <t>1241107; 1333129</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1166831; 1260274</t>
+          <t>1166354; 1256625</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>573066; 990756</t>
+          <t>576241; 987734</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>306371; 360027</t>
+          <t>308752; 360595</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>351302; 407897</t>
+          <t>350128; 409966</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>341370; 400636</t>
+          <t>339964; 398466</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>255219; 320441</t>
+          <t>260277; 318375</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>411672; 461619</t>
+          <t>409990; 459154</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>497673; 550667</t>
+          <t>498971; 550387</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>443159; 500724</t>
+          <t>443761; 499972</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>377836; 704418</t>
+          <t>372261; 717153</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>732848; 807226</t>
+          <t>734462; 809810</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>864048; 944540</t>
+          <t>869752; 949109</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>803803; 884577</t>
+          <t>799650; 878556</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>665910; 1080693</t>
+          <t>658842; 1073526</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>407957; 468301</t>
+          <t>410052; 469224</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>517682; 579616</t>
+          <t>514485; 576712</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>488628; 548105</t>
+          <t>490550; 547475</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>320382; 386343</t>
+          <t>324603; 388349</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>626819; 690102</t>
+          <t>621910; 687754</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>689746; 751355</t>
+          <t>689400; 751385</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>629423; 692434</t>
+          <t>629484; 694785</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>372735; 506020</t>
+          <t>379906; 511462</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1053860; 1140327</t>
+          <t>1048611; 1138298</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1225261; 1311379</t>
+          <t>1221093; 1311133</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1136745; 1225110</t>
+          <t>1136241; 1222061</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>719221; 871687</t>
+          <t>723580; 873317</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1519872; 1638673</t>
+          <t>1520616; 1636835</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1849476; 1968067</t>
+          <t>1850019; 1965044</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1712701; 1832928</t>
+          <t>1714718; 1829476</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1045718; 1448031</t>
+          <t>1022275; 1443659</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2100896; 2222608</t>
+          <t>2105314; 2214989</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2403543; 2519341</t>
+          <t>2409124; 2519358</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2202021; 2314803</t>
+          <t>2204921; 2318325</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1639887; 2155738</t>
+          <t>1633608; 2158123</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3652324; 3821214</t>
+          <t>3655098; 3821684</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4285196; 4452118</t>
+          <t>4292739; 4457638</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3949120; 4116959</t>
+          <t>3954961; 4114052</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2816485; 3464703</t>
+          <t>2822782; 3424282</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P2A_R-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>43,57%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>45,61%</t>
+          <t>49,19%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>46,47%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>44,47; 52,49</t>
+          <t>44,88; 52,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>56,69; 64,23</t>
+          <t>56,44; 64,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>49,13; 57,07</t>
+          <t>48,88; 56,84</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>40,61; 49,36</t>
+          <t>39,63; 47,67</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>59,44; 66,89</t>
+          <t>59,35; 66,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,98; 72,39</t>
+          <t>65,42; 72,65</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>61,69; 69,18</t>
+          <t>61,98; 69,35</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>35,99; 50,06</t>
+          <t>45,88; 52,14</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>53,32; 58,26</t>
+          <t>52,87; 58,22</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>62,13; 67,56</t>
+          <t>62,28; 67,59</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>56,55; 61,97</t>
+          <t>56,53; 61,74</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>39,8; 48,21</t>
+          <t>44,05; 49,06</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>48,87%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>44,53%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>45,24; 51,77</t>
+          <t>45,25; 52,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>51,1; 57,43</t>
+          <t>51,01; 57,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>48,75; 55,09</t>
+          <t>48,64; 54,93</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15,21; 42,2</t>
+          <t>36,84; 43,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>62,0; 68,4</t>
+          <t>62,01; 68,34</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>67,89; 74,05</t>
+          <t>68,2; 74,07</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>62,52; 68,66</t>
+          <t>62,42; 68,39</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>46,68; 52,38</t>
+          <t>46,19; 51,63</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>54,72; 59,16</t>
+          <t>54,84; 59,34</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>60,54; 65,03</t>
+          <t>60,56; 64,89</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>56,47; 60,84</t>
+          <t>56,39; 60,61</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>26,78; 45,91</t>
+          <t>42,51; 46,57</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>54,55%</t>
+          <t>42,76%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>41,2%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>45,5; 53,15</t>
+          <t>45,23; 53,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>46,21; 54,11</t>
+          <t>46,41; 53,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>44,76; 52,46</t>
+          <t>44,33; 52,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>36,94; 45,18</t>
+          <t>35,82; 44,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>59,95; 67,14</t>
+          <t>59,93; 67,12</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>64,2; 70,82</t>
+          <t>64,07; 70,85</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>56,53; 63,69</t>
+          <t>56,24; 63,55</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>39,88; 76,84</t>
+          <t>39,69; 45,83</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>53,91; 59,44</t>
+          <t>53,67; 59,27</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>56,67; 61,84</t>
+          <t>56,32; 61,72</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>51,77; 56,88</t>
+          <t>51,75; 56,9</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>40,22; 65,54</t>
+          <t>38,72; 43,85</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>40,54%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>43,52; 49,8</t>
+          <t>43,24; 49,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>54,29; 60,85</t>
+          <t>54,52; 61,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>52,32; 58,39</t>
+          <t>52,36; 58,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>35,02; 41,9</t>
+          <t>33,18; 39,51</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>59,88; 66,22</t>
+          <t>60,06; 66,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,54; 71,43</t>
+          <t>65,63; 71,3</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>60,31; 66,56</t>
+          <t>60,61; 66,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>34,7; 46,71</t>
+          <t>41,81; 46,82</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>52,94; 57,47</t>
+          <t>53,11; 57,4</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>61,07; 65,57</t>
+          <t>61,43; 65,63</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>57,35; 61,68</t>
+          <t>57,08; 61,79</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>35,79; 43,2</t>
+          <t>38,76; 42,64</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>39,57%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>43,01%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>46,41; 49,96</t>
+          <t>46,5; 50,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>53,99; 57,34</t>
+          <t>53,81; 57,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>50,52; 53,9</t>
+          <t>50,34; 53,93</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29,55; 41,73</t>
+          <t>37,91; 41,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>62,3; 65,55</t>
+          <t>62,11; 65,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>67,7; 70,8</t>
+          <t>67,48; 70,74</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>62,21; 65,41</t>
+          <t>62,08; 65,28</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>44,01; 58,13</t>
+          <t>44,93; 47,78</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>54,92; 57,42</t>
+          <t>54,84; 57,32</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>61,46; 63,82</t>
+          <t>61,34; 63,73</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>57,0; 59,29</t>
+          <t>56,89; 59,25</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>39,36; 47,74</t>
+          <t>41,85; 44,24</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>284071</t>
+          <t>300935</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>330829</t>
+          <t>361177</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>614901</t>
+          <t>662112</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>308637; 364262</t>
+          <t>311451; 363450</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>398779; 451848</t>
+          <t>397057; 450330</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>331525; 385093</t>
+          <t>329844; 383568</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>258070; 313631</t>
+          <t>273749; 329227</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>409157; 460426</t>
+          <t>408522; 456927</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>452926; 504629</t>
+          <t>455989; 506415</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>415093; 465442</t>
+          <t>417043; 466636</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>261082; 363125</t>
+          <t>336852; 382817</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>737037; 805344</t>
+          <t>730913; 804762</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>870207; 946130</t>
+          <t>872180; 946577</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>762039; 835145</t>
+          <t>761759; 831993</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>541519; 656008</t>
+          <t>627636; 699053</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>391011</t>
+          <t>420519</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>473577</t>
+          <t>523631</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>864588</t>
+          <t>944150</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>435150; 497966</t>
+          <t>435201; 502082</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>520121; 584564</t>
+          <t>519275; 587764</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>498445; 563291</t>
+          <t>497265; 561663</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>181488; 503370</t>
+          <t>386435; 453953</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>600389; 662363</t>
+          <t>600509; 661815</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>700743; 764296</t>
+          <t>703917; 764521</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>651986; 716049</t>
+          <t>650969; 713222</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>447500; 502155</t>
+          <t>494917; 553149</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1056142; 1141980</t>
+          <t>1058493; 1145308</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1241107; 1333129</t>
+          <t>1241620; 1330245</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1166354; 1256625</t>
+          <t>1164641; 1251799</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>576241; 987734</t>
+          <t>901380; 987527</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>289201</t>
+          <t>318142</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>509113</t>
+          <t>347322</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>798314</t>
+          <t>665464</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>308752; 360595</t>
+          <t>306902; 361990</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>350128; 409966</t>
+          <t>351599; 408665</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>339964; 398466</t>
+          <t>336703; 397284</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>260277; 318375</t>
+          <t>287694; 353978</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>409990; 459154</t>
+          <t>409809; 458994</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>498971; 550387</t>
+          <t>497972; 550662</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>443761; 499972</t>
+          <t>441465; 498839</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>372261; 717153</t>
+          <t>322365; 372263</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>734462; 809810</t>
+          <t>731204; 807523</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>869752; 949109</t>
+          <t>864350; 947312</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>799650; 878556</t>
+          <t>799318; 878806</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>658842; 1073526</t>
+          <t>625487; 708390</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>354490</t>
+          <t>358387</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>465298</t>
+          <t>496659</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>819789</t>
+          <t>855046</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>410052; 469224</t>
+          <t>407459; 466706</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>514485; 576712</t>
+          <t>516745; 578901</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>490550; 547475</t>
+          <t>490871; 548932</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>324603; 388349</t>
+          <t>328508; 391134</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>621910; 687754</t>
+          <t>623820; 687299</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>689400; 751385</t>
+          <t>690340; 750045</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>629484; 694785</t>
+          <t>632656; 696784</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>379906; 511462</t>
+          <t>467825; 523900</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1048611; 1138298</t>
+          <t>1051989; 1137007</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1221093; 1311133</t>
+          <t>1228292; 1312456</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1136241; 1222061</t>
+          <t>1130949; 1224221</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>723580; 873317</t>
+          <t>817476; 899221</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1318774</t>
+          <t>1397982</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1778817</t>
+          <t>1728788</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3097592</t>
+          <t>3126771</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1520616; 1636835</t>
+          <t>1523547; 1639290</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1850019; 1965044</t>
+          <t>1844031; 1970458</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1714718; 1829476</t>
+          <t>1708608; 1830690</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1022275; 1443659</t>
+          <t>1339425; 1464117</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2105314; 2214989</t>
+          <t>2098769; 2211245</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2409124; 2519358</t>
+          <t>2401120; 2517117</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2204921; 2318325</t>
+          <t>2200429; 2313834</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1633608; 2158123</t>
+          <t>1679038; 1785648</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3655098; 3821684</t>
+          <t>3649928; 3815091</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4292739; 4457638</t>
+          <t>4284597; 4451431</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3954961; 4114052</t>
+          <t>3947609; 4111313</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2822782; 3424282</t>
+          <t>3042214; 3215997</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P2A_R-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares que tienen personas con alguna condición, enfermedad crónica o limitación (tasa de respuesta: 100,0%)</t>
+          <t>Población que convive con personas con alguna condición, enfermedad crónica o limitación (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares que tienen personas con alguna condición, enfermedad crónica o limitación (tasa de respuesta: 100,0%)</t>
+          <t>Población que convive con personas con alguna condición, enfermedad crónica o limitación (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
